--- a/Proyecto_Final_Unificado - UMG/Algoritmos/Ventas.xlsx
+++ b/Proyecto_Final_Unificado - UMG/Algoritmos/Ventas.xlsx
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
